--- a/AlgorithmNData/Bug Algorithms Full Documented Values.xlsx
+++ b/AlgorithmNData/Bug Algorithms Full Documented Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utrgv-my.sharepoint.com/personal/izabella_valero01_utrgv_edu/Documents/Desktop/MARS Research/May20-PathPlanning/My_Work/Typed Reports/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utrgv-my.sharepoint.com/personal/izabella_valero01_utrgv_edu/Documents/Desktop/MARS Research/May20-PathPlanning/webots/mars-github-bug-algorithms/bug_algorithms/AlgorithmNData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1193" documentId="8_{3A44FF85-21B8-4464-9902-83D39A64E269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C34BDE7-90CE-40BA-A3C3-B189488E0301}"/>
+  <xr:revisionPtr revIDLastSave="1214" documentId="8_{3A44FF85-21B8-4464-9902-83D39A64E269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A08C817-3DB1-4618-B7F1-3433423008CB}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{1B981E3A-1744-4B50-BA68-B582BA61DD63}"/>
+    <workbookView xWindow="7973" yWindow="15" windowWidth="14527" windowHeight="11115" xr2:uid="{1B981E3A-1744-4B50-BA68-B582BA61DD63}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -513,7 +513,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -557,36 +557,11 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -612,6 +587,30 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10253,40 +10252,19 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:62" x14ac:dyDescent="0.45">
-      <c r="A3" s="37"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
     </row>
-    <row r="4" spans="1:62" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="38"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-    </row>
+    <row r="4" spans="1:62" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="5" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="38"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
       <c r="O5" t="s">
         <v>42</v>
       </c>
@@ -10295,16 +10273,6 @@
       </c>
     </row>
     <row r="6" spans="1:62" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="38"/>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
       <c r="N6" t="s">
         <v>35</v>
       </c>
@@ -10319,16 +10287,6 @@
       </c>
     </row>
     <row r="7" spans="1:62" x14ac:dyDescent="0.45">
-      <c r="A7" s="38"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
       <c r="N7" t="s">
         <v>36</v>
       </c>
@@ -10343,16 +10301,6 @@
       </c>
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.45">
-      <c r="A8" s="38"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
       <c r="N8" t="s">
         <v>37</v>
       </c>
@@ -10367,16 +10315,6 @@
       </c>
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.45">
-      <c r="A9" s="38"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
       <c r="N9" t="s">
         <v>38</v>
       </c>
@@ -10391,16 +10329,6 @@
       </c>
     </row>
     <row r="10" spans="1:62" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="38"/>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="38"/>
       <c r="N10" t="s">
         <v>39</v>
       </c>
@@ -10415,16 +10343,6 @@
       </c>
     </row>
     <row r="11" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="38"/>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="38"/>
       <c r="N11" t="s">
         <v>40</v>
       </c>
@@ -10478,16 +10396,6 @@
       </c>
     </row>
     <row r="12" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="38"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
       <c r="N12" t="s">
         <v>41</v>
       </c>
@@ -10544,16 +10452,13 @@
       </c>
     </row>
     <row r="13" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="37"/>
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
       <c r="O13" s="14"/>
       <c r="AP13" t="s">
         <v>36</v>
@@ -10599,16 +10504,6 @@
       </c>
     </row>
     <row r="14" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="38"/>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="38"/>
       <c r="AP14" t="s">
         <v>37</v>
       </c>
@@ -10653,16 +10548,6 @@
       </c>
     </row>
     <row r="15" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="38"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
       <c r="P15" s="9" t="s">
         <v>43</v>
       </c>
@@ -10722,17 +10607,7 @@
       </c>
     </row>
     <row r="16" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="38"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="N16" s="29" t="s">
+      <c r="N16" s="43" t="s">
         <v>35</v>
       </c>
       <c r="O16" s="1" t="s">
@@ -10741,7 +10616,7 @@
       <c r="P16" s="12">
         <v>72.77</v>
       </c>
-      <c r="R16" s="29" t="s">
+      <c r="R16" s="43" t="s">
         <v>35</v>
       </c>
       <c r="S16" s="3" t="s">
@@ -10750,7 +10625,7 @@
       <c r="T16" s="14">
         <v>36.29</v>
       </c>
-      <c r="V16" s="29" t="s">
+      <c r="V16" s="43" t="s">
         <v>35</v>
       </c>
       <c r="W16" s="1" t="s">
@@ -10809,31 +10684,21 @@
       </c>
     </row>
     <row r="17" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="38"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="N17" s="29"/>
+      <c r="N17" s="43"/>
       <c r="O17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="P17" s="14">
         <v>48.86</v>
       </c>
-      <c r="R17" s="29"/>
+      <c r="R17" s="43"/>
       <c r="S17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="T17" s="14">
         <v>77.44</v>
       </c>
-      <c r="V17" s="29"/>
+      <c r="V17" s="43"/>
       <c r="W17" s="3" t="s">
         <v>22</v>
       </c>
@@ -10890,17 +10755,7 @@
       </c>
     </row>
     <row r="18" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="38"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="N18" s="29" t="s">
+      <c r="N18" s="43" t="s">
         <v>36</v>
       </c>
       <c r="O18" s="1" t="s">
@@ -10909,14 +10764,14 @@
       <c r="P18" s="12">
         <v>75.84</v>
       </c>
-      <c r="R18" s="29"/>
+      <c r="R18" s="43"/>
       <c r="S18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="T18" s="14">
         <v>96.03</v>
       </c>
-      <c r="V18" s="29"/>
+      <c r="V18" s="43"/>
       <c r="W18" s="3" t="s">
         <v>23</v>
       </c>
@@ -10973,24 +10828,14 @@
       </c>
     </row>
     <row r="19" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="38"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
-      <c r="N19" s="29"/>
+      <c r="N19" s="43"/>
       <c r="O19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="P19" s="14">
         <v>64.19</v>
       </c>
-      <c r="R19" s="29" t="s">
+      <c r="R19" s="43" t="s">
         <v>36</v>
       </c>
       <c r="S19" s="3" t="s">
@@ -10999,7 +10844,7 @@
       <c r="T19" s="14">
         <v>56.54</v>
       </c>
-      <c r="V19" s="29" t="s">
+      <c r="V19" s="43" t="s">
         <v>36</v>
       </c>
       <c r="W19" s="1" t="s">
@@ -11016,17 +10861,7 @@
       </c>
     </row>
     <row r="20" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="38"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
-      <c r="N20" s="29" t="s">
+      <c r="N20" s="43" t="s">
         <v>37</v>
       </c>
       <c r="O20" s="1" t="s">
@@ -11035,14 +10870,14 @@
       <c r="P20" s="12">
         <v>75.84</v>
       </c>
-      <c r="R20" s="29"/>
+      <c r="R20" s="43"/>
       <c r="S20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="T20" s="14">
         <v>80.64</v>
       </c>
-      <c r="V20" s="29"/>
+      <c r="V20" s="43"/>
       <c r="W20" s="3" t="s">
         <v>22</v>
       </c>
@@ -11057,31 +10892,21 @@
       </c>
     </row>
     <row r="21" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A21" s="38"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
-      <c r="N21" s="29"/>
+      <c r="N21" s="43"/>
       <c r="O21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="P21" s="14">
         <v>63.19</v>
       </c>
-      <c r="R21" s="29"/>
+      <c r="R21" s="43"/>
       <c r="S21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="T21" s="14">
         <v>121.95</v>
       </c>
-      <c r="V21" s="29"/>
+      <c r="V21" s="43"/>
       <c r="W21" s="3" t="s">
         <v>23</v>
       </c>
@@ -11096,17 +10921,7 @@
       </c>
     </row>
     <row r="22" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="38"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="N22" s="29" t="s">
+      <c r="N22" s="43" t="s">
         <v>38</v>
       </c>
       <c r="O22" s="1" t="s">
@@ -11115,7 +10930,7 @@
       <c r="P22" s="12">
         <v>72.77</v>
       </c>
-      <c r="R22" s="29" t="s">
+      <c r="R22" s="43" t="s">
         <v>37</v>
       </c>
       <c r="S22" s="3" t="s">
@@ -11124,7 +10939,7 @@
       <c r="T22" s="14">
         <v>56.54</v>
       </c>
-      <c r="V22" s="29" t="s">
+      <c r="V22" s="43" t="s">
         <v>37</v>
       </c>
       <c r="W22" s="1" t="s">
@@ -11141,31 +10956,21 @@
       </c>
     </row>
     <row r="23" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A23" s="38"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="N23" s="29"/>
+      <c r="N23" s="43"/>
       <c r="O23" s="3" t="s">
         <v>22</v>
       </c>
       <c r="P23" s="14">
         <v>48.86</v>
       </c>
-      <c r="R23" s="29"/>
+      <c r="R23" s="43"/>
       <c r="S23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="T23" s="14">
         <v>82.53</v>
       </c>
-      <c r="V23" s="29"/>
+      <c r="V23" s="43"/>
       <c r="W23" s="3" t="s">
         <v>22</v>
       </c>
@@ -11180,7 +10985,7 @@
       </c>
     </row>
     <row r="24" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="N24" s="29" t="s">
+      <c r="N24" s="43" t="s">
         <v>39</v>
       </c>
       <c r="O24" s="1" t="s">
@@ -11189,14 +10994,14 @@
       <c r="P24" s="12">
         <v>76.03</v>
       </c>
-      <c r="R24" s="29"/>
+      <c r="R24" s="43"/>
       <c r="S24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="T24" s="14">
         <v>162.11000000000001</v>
       </c>
-      <c r="V24" s="29"/>
+      <c r="V24" s="43"/>
       <c r="W24" s="3" t="s">
         <v>23</v>
       </c>
@@ -11211,14 +11016,14 @@
       </c>
     </row>
     <row r="25" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="N25" s="29"/>
+      <c r="N25" s="43"/>
       <c r="O25" s="3" t="s">
         <v>22</v>
       </c>
       <c r="P25" s="14">
         <v>120.51</v>
       </c>
-      <c r="R25" s="29" t="s">
+      <c r="R25" s="43" t="s">
         <v>38</v>
       </c>
       <c r="S25" s="3" t="s">
@@ -11227,7 +11032,7 @@
       <c r="T25" s="14">
         <v>36.130000000000003</v>
       </c>
-      <c r="V25" s="29" t="s">
+      <c r="V25" s="43" t="s">
         <v>38</v>
       </c>
       <c r="W25" s="1" t="s">
@@ -11244,20 +11049,20 @@
       </c>
     </row>
     <row r="26" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="33"/>
-      <c r="N26" s="29" t="s">
+      <c r="B26" s="49"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="50"/>
+      <c r="N26" s="43" t="s">
         <v>40</v>
       </c>
       <c r="O26" s="1" t="s">
@@ -11266,14 +11071,14 @@
       <c r="P26" s="12">
         <v>67.260000000000005</v>
       </c>
-      <c r="R26" s="29"/>
+      <c r="R26" s="43"/>
       <c r="S26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="T26" s="14">
         <v>77.44</v>
       </c>
-      <c r="V26" s="29"/>
+      <c r="V26" s="43"/>
       <c r="W26" s="3" t="s">
         <v>22</v>
       </c>
@@ -11317,21 +11122,21 @@
       <c r="K27" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="N27" s="29"/>
+      <c r="N27" s="43"/>
       <c r="O27" s="3" t="s">
         <v>22</v>
       </c>
       <c r="P27" s="14">
         <v>109.92</v>
       </c>
-      <c r="R27" s="29"/>
+      <c r="R27" s="43"/>
       <c r="S27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="T27" s="14">
         <v>155.26</v>
       </c>
-      <c r="V27" s="29"/>
+      <c r="V27" s="43"/>
       <c r="W27" s="3" t="s">
         <v>23</v>
       </c>
@@ -11346,7 +11151,7 @@
       </c>
     </row>
     <row r="28" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A28" s="27" t="s">
+      <c r="A28" s="44" t="s">
         <v>9</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -11357,15 +11162,15 @@
       <c r="E28" s="12">
         <v>72.77</v>
       </c>
-      <c r="F28" s="42"/>
-      <c r="G28" s="34"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="27"/>
       <c r="H28" s="12">
         <v>95.23</v>
       </c>
       <c r="I28" s="12"/>
       <c r="J28" s="13"/>
       <c r="K28" s="12"/>
-      <c r="N28" s="29" t="s">
+      <c r="N28" s="43" t="s">
         <v>41</v>
       </c>
       <c r="O28" s="1" t="s">
@@ -11374,7 +11179,7 @@
       <c r="P28" s="14">
         <v>66.27</v>
       </c>
-      <c r="R28" s="29" t="s">
+      <c r="R28" s="43" t="s">
         <v>39</v>
       </c>
       <c r="S28" s="3" t="s">
@@ -11383,7 +11188,7 @@
       <c r="T28" s="14">
         <v>103.04</v>
       </c>
-      <c r="V28" s="29" t="s">
+      <c r="V28" s="43" t="s">
         <v>39</v>
       </c>
       <c r="W28" s="1" t="s">
@@ -11400,7 +11205,7 @@
       </c>
     </row>
     <row r="29" spans="1:62" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="28"/>
+      <c r="A29" s="45"/>
       <c r="B29" s="3" t="s">
         <v>22</v>
       </c>
@@ -11413,31 +11218,31 @@
       <c r="E29" s="14">
         <v>48.86</v>
       </c>
-      <c r="F29" s="35">
+      <c r="F29" s="28">
         <v>36.29</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="27"/>
       <c r="H29" s="14">
         <v>66.400000000000006</v>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="16"/>
       <c r="K29" s="14"/>
-      <c r="N29" s="29"/>
+      <c r="N29" s="43"/>
       <c r="O29" s="3" t="s">
         <v>22</v>
       </c>
       <c r="P29" s="14">
         <v>40.51</v>
       </c>
-      <c r="R29" s="29"/>
+      <c r="R29" s="43"/>
       <c r="S29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="T29" s="14">
         <v>74.19</v>
       </c>
-      <c r="V29" s="29"/>
+      <c r="V29" s="43"/>
       <c r="W29" s="3" t="s">
         <v>22</v>
       </c>
@@ -11446,29 +11251,29 @@
       </c>
     </row>
     <row r="30" spans="1:62" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A30" s="28"/>
+      <c r="A30" s="45"/>
       <c r="B30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C30" s="18"/>
       <c r="D30" s="20"/>
       <c r="E30" s="24"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="27"/>
       <c r="H30" s="14">
         <v>83.65</v>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="16"/>
       <c r="K30" s="14"/>
-      <c r="R30" s="29"/>
+      <c r="R30" s="43"/>
       <c r="S30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="T30" s="14">
         <v>37.31</v>
       </c>
-      <c r="V30" s="29"/>
+      <c r="V30" s="43"/>
       <c r="W30" s="3" t="s">
         <v>23</v>
       </c>
@@ -11477,17 +11282,17 @@
       </c>
     </row>
     <row r="31" spans="1:62" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="28"/>
+      <c r="A31" s="45"/>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="18"/>
       <c r="D31" s="20"/>
       <c r="E31" s="24"/>
-      <c r="F31" s="35">
+      <c r="F31" s="28">
         <v>77.44</v>
       </c>
-      <c r="G31" s="35">
+      <c r="G31" s="28">
         <v>155.71</v>
       </c>
       <c r="H31" s="20"/>
@@ -11496,7 +11301,7 @@
       </c>
       <c r="J31" s="16"/>
       <c r="K31" s="14"/>
-      <c r="R31" s="29" t="s">
+      <c r="R31" s="43" t="s">
         <v>40</v>
       </c>
       <c r="S31" s="3" t="s">
@@ -11505,7 +11310,7 @@
       <c r="T31" s="14">
         <v>81.790000000000006</v>
       </c>
-      <c r="V31" s="29" t="s">
+      <c r="V31" s="43" t="s">
         <v>40</v>
       </c>
       <c r="W31" s="1" t="s">
@@ -11516,31 +11321,31 @@
       </c>
     </row>
     <row r="32" spans="1:62" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A32" s="28"/>
+      <c r="A32" s="45"/>
       <c r="B32" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C32" s="18"/>
       <c r="D32" s="20"/>
       <c r="E32" s="24"/>
-      <c r="F32" s="44">
+      <c r="F32" s="35">
         <v>96.03</v>
       </c>
-      <c r="G32" s="35">
+      <c r="G32" s="28">
         <v>243.65</v>
       </c>
       <c r="H32" s="20"/>
       <c r="I32" s="14"/>
       <c r="J32" s="16"/>
       <c r="K32" s="14"/>
-      <c r="R32" s="29"/>
+      <c r="R32" s="43"/>
       <c r="S32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="T32" s="14">
         <v>72.77</v>
       </c>
-      <c r="V32" s="29"/>
+      <c r="V32" s="43"/>
       <c r="W32" s="3" t="s">
         <v>22</v>
       </c>
@@ -11549,7 +11354,7 @@
       </c>
     </row>
     <row r="33" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A33" s="27" t="s">
+      <c r="A33" s="44" t="s">
         <v>10</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -11560,22 +11365,22 @@
       <c r="E33" s="12">
         <v>75.84</v>
       </c>
-      <c r="F33" s="42"/>
+      <c r="F33" s="33"/>
       <c r="G33" s="17"/>
-      <c r="H33" s="41">
+      <c r="H33" s="32">
         <v>111.42</v>
       </c>
       <c r="I33" s="12"/>
       <c r="J33" s="13"/>
       <c r="K33" s="12"/>
-      <c r="R33" s="29"/>
+      <c r="R33" s="43"/>
       <c r="S33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="T33" s="14">
         <v>28.61</v>
       </c>
-      <c r="V33" s="29"/>
+      <c r="V33" s="43"/>
       <c r="W33" s="3" t="s">
         <v>23</v>
       </c>
@@ -11590,7 +11395,7 @@
       </c>
     </row>
     <row r="34" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A34" s="28"/>
+      <c r="A34" s="45"/>
       <c r="B34" s="3" t="s">
         <v>22</v>
       </c>
@@ -11603,11 +11408,11 @@
       <c r="E34" s="14">
         <v>64.19</v>
       </c>
-      <c r="F34" s="35">
+      <c r="F34" s="28">
         <v>56.54</v>
       </c>
       <c r="G34" s="24"/>
-      <c r="H34" s="35">
+      <c r="H34" s="28">
         <v>94.18</v>
       </c>
       <c r="I34" s="14"/>
@@ -11616,7 +11421,7 @@
       <c r="P34" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="R34" s="29" t="s">
+      <c r="R34" s="43" t="s">
         <v>41</v>
       </c>
       <c r="S34" s="3" t="s">
@@ -11625,7 +11430,7 @@
       <c r="T34" s="14">
         <v>36.32</v>
       </c>
-      <c r="V34" s="29" t="s">
+      <c r="V34" s="43" t="s">
         <v>41</v>
       </c>
       <c r="W34" s="1" t="s">
@@ -11642,22 +11447,22 @@
       </c>
     </row>
     <row r="35" spans="1:62" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="28"/>
+      <c r="A35" s="45"/>
       <c r="B35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C35" s="18"/>
       <c r="D35" s="20"/>
       <c r="E35" s="24"/>
-      <c r="F35" s="43"/>
+      <c r="F35" s="34"/>
       <c r="G35" s="24"/>
-      <c r="H35" s="35">
+      <c r="H35" s="28">
         <v>116.22</v>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="16"/>
       <c r="K35" s="14"/>
-      <c r="N35" s="29" t="s">
+      <c r="N35" s="43" t="s">
         <v>35</v>
       </c>
       <c r="O35" s="3" t="s">
@@ -11666,14 +11471,14 @@
       <c r="P35" s="14">
         <v>155.71</v>
       </c>
-      <c r="R35" s="29"/>
+      <c r="R35" s="43"/>
       <c r="S35" s="3" t="s">
         <v>24</v>
       </c>
       <c r="T35" s="14">
         <v>74.75</v>
       </c>
-      <c r="V35" s="29"/>
+      <c r="V35" s="43"/>
       <c r="W35" s="3" t="s">
         <v>22</v>
       </c>
@@ -11688,40 +11493,40 @@
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.45">
-      <c r="A36" s="28"/>
+      <c r="A36" s="45"/>
       <c r="B36" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C36" s="18"/>
       <c r="D36" s="20"/>
       <c r="E36" s="24"/>
-      <c r="F36" s="35">
+      <c r="F36" s="28">
         <v>80.64</v>
       </c>
       <c r="G36" s="14">
         <v>120.93</v>
       </c>
-      <c r="H36" s="34"/>
+      <c r="H36" s="27"/>
       <c r="I36" s="14">
         <v>56.32</v>
       </c>
       <c r="J36" s="16"/>
       <c r="K36" s="14"/>
-      <c r="N36" s="29"/>
+      <c r="N36" s="43"/>
       <c r="O36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="P36" s="14">
         <v>243.65</v>
       </c>
-      <c r="R36" s="29"/>
+      <c r="R36" s="43"/>
       <c r="S36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="T36" s="14">
         <v>93.73</v>
       </c>
-      <c r="V36" s="29"/>
+      <c r="V36" s="43"/>
       <c r="W36" s="3" t="s">
         <v>23</v>
       </c>
@@ -11736,24 +11541,24 @@
       </c>
     </row>
     <row r="37" spans="1:62" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A37" s="28"/>
+      <c r="A37" s="45"/>
       <c r="B37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C37" s="18"/>
       <c r="D37" s="20"/>
       <c r="E37" s="24"/>
-      <c r="F37" s="44">
+      <c r="F37" s="35">
         <v>121.95</v>
       </c>
-      <c r="G37" s="45">
+      <c r="G37" s="36">
         <v>272.77</v>
       </c>
-      <c r="H37" s="34"/>
+      <c r="H37" s="27"/>
       <c r="I37" s="14"/>
       <c r="J37" s="16"/>
       <c r="K37" s="14"/>
-      <c r="N37" s="29" t="s">
+      <c r="N37" s="43" t="s">
         <v>36</v>
       </c>
       <c r="O37" s="3" t="s">
@@ -11764,7 +11569,7 @@
       </c>
     </row>
     <row r="38" spans="1:62" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="28" t="s">
+      <c r="A38" s="45" t="s">
         <v>11</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -11775,7 +11580,7 @@
       <c r="E38" s="12">
         <v>75.84</v>
       </c>
-      <c r="F38" s="42"/>
+      <c r="F38" s="33"/>
       <c r="G38" s="17"/>
       <c r="H38" s="12">
         <v>111.42</v>
@@ -11783,7 +11588,7 @@
       <c r="I38" s="12"/>
       <c r="J38" s="13"/>
       <c r="K38" s="12"/>
-      <c r="N38" s="29"/>
+      <c r="N38" s="43"/>
       <c r="O38" s="3" t="s">
         <v>25</v>
       </c>
@@ -11792,7 +11597,7 @@
       </c>
     </row>
     <row r="39" spans="1:62" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A39" s="28"/>
+      <c r="A39" s="45"/>
       <c r="B39" s="3" t="s">
         <v>22</v>
       </c>
@@ -11815,7 +11620,7 @@
       <c r="I39" s="14"/>
       <c r="J39" s="16"/>
       <c r="K39" s="14"/>
-      <c r="N39" s="29" t="s">
+      <c r="N39" s="43" t="s">
         <v>37</v>
       </c>
       <c r="O39" s="3" t="s">
@@ -11826,7 +11631,7 @@
       </c>
     </row>
     <row r="40" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A40" s="28"/>
+      <c r="A40" s="45"/>
       <c r="B40" s="3" t="s">
         <v>23</v>
       </c>
@@ -11841,7 +11646,7 @@
       <c r="I40" s="14"/>
       <c r="J40" s="16"/>
       <c r="K40" s="14"/>
-      <c r="N40" s="29"/>
+      <c r="N40" s="43"/>
       <c r="O40" s="3" t="s">
         <v>25</v>
       </c>
@@ -11853,7 +11658,7 @@
       </c>
     </row>
     <row r="41" spans="1:62" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="28"/>
+      <c r="A41" s="45"/>
       <c r="B41" s="3" t="s">
         <v>24</v>
       </c>
@@ -11872,7 +11677,7 @@
       </c>
       <c r="J41" s="16"/>
       <c r="K41" s="14"/>
-      <c r="N41" s="29" t="s">
+      <c r="N41" s="43" t="s">
         <v>38</v>
       </c>
       <c r="O41" s="3" t="s">
@@ -11889,24 +11694,24 @@
       </c>
     </row>
     <row r="42" spans="1:62" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A42" s="28"/>
+      <c r="A42" s="45"/>
       <c r="B42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C42" s="18"/>
       <c r="D42" s="20"/>
       <c r="E42" s="20"/>
-      <c r="F42" s="45">
+      <c r="F42" s="36">
         <v>162.11000000000001</v>
       </c>
-      <c r="G42" s="45">
+      <c r="G42" s="36">
         <v>301.92</v>
       </c>
       <c r="H42" s="20"/>
       <c r="I42" s="14"/>
       <c r="J42" s="16"/>
       <c r="K42" s="14"/>
-      <c r="N42" s="29"/>
+      <c r="N42" s="43"/>
       <c r="O42" s="3" t="s">
         <v>25</v>
       </c>
@@ -11921,7 +11726,7 @@
       </c>
     </row>
     <row r="43" spans="1:62" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="27" t="s">
+      <c r="A43" s="44" t="s">
         <v>12</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -11940,7 +11745,7 @@
       <c r="I43" s="12"/>
       <c r="J43" s="13"/>
       <c r="K43" s="12"/>
-      <c r="N43" s="29" t="s">
+      <c r="N43" s="43" t="s">
         <v>39</v>
       </c>
       <c r="O43" s="3" t="s">
@@ -11957,7 +11762,7 @@
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.45">
-      <c r="A44" s="28"/>
+      <c r="A44" s="45"/>
       <c r="B44" s="3" t="s">
         <v>22</v>
       </c>
@@ -11980,7 +11785,7 @@
       <c r="I44" s="14"/>
       <c r="J44" s="16"/>
       <c r="K44" s="14"/>
-      <c r="N44" s="29"/>
+      <c r="N44" s="43"/>
       <c r="O44" s="3" t="s">
         <v>25</v>
       </c>
@@ -11995,7 +11800,7 @@
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.45">
-      <c r="A45" s="28"/>
+      <c r="A45" s="45"/>
       <c r="B45" s="3" t="s">
         <v>23</v>
       </c>
@@ -12010,7 +11815,7 @@
       <c r="I45" s="14"/>
       <c r="J45" s="16"/>
       <c r="K45" s="14"/>
-      <c r="N45" s="29" t="s">
+      <c r="N45" s="43" t="s">
         <v>40</v>
       </c>
       <c r="O45" s="3" t="s">
@@ -12027,7 +11832,7 @@
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.45">
-      <c r="A46" s="28"/>
+      <c r="A46" s="45"/>
       <c r="B46" s="3" t="s">
         <v>24</v>
       </c>
@@ -12046,7 +11851,7 @@
       </c>
       <c r="J46" s="16"/>
       <c r="K46" s="14"/>
-      <c r="N46" s="29"/>
+      <c r="N46" s="43"/>
       <c r="O46" s="3" t="s">
         <v>25</v>
       </c>
@@ -12061,24 +11866,24 @@
       </c>
     </row>
     <row r="47" spans="1:62" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A47" s="28"/>
+      <c r="A47" s="45"/>
       <c r="B47" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C47" s="18"/>
       <c r="D47" s="20"/>
       <c r="E47" s="20"/>
-      <c r="F47" s="45">
+      <c r="F47" s="36">
         <v>155.26</v>
       </c>
-      <c r="G47" s="45">
+      <c r="G47" s="36">
         <v>282.66000000000003</v>
       </c>
       <c r="H47" s="20"/>
       <c r="I47" s="14"/>
       <c r="J47" s="16"/>
       <c r="K47" s="14"/>
-      <c r="N47" s="29" t="s">
+      <c r="N47" s="43" t="s">
         <v>41</v>
       </c>
       <c r="O47" s="3" t="s">
@@ -12095,7 +11900,7 @@
       </c>
     </row>
     <row r="48" spans="1:62" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="44" t="s">
         <v>13</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -12114,7 +11919,7 @@
       <c r="I48" s="12"/>
       <c r="J48" s="13"/>
       <c r="K48" s="12"/>
-      <c r="N48" s="29"/>
+      <c r="N48" s="43"/>
       <c r="O48" s="3" t="s">
         <v>25</v>
       </c>
@@ -12122,8 +11927,8 @@
         <v>238.53</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A49" s="28"/>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A49" s="45"/>
       <c r="B49" s="3" t="s">
         <v>22</v>
       </c>
@@ -12147,8 +11952,8 @@
       <c r="J49" s="16"/>
       <c r="K49" s="14"/>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A50" s="28"/>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A50" s="45"/>
       <c r="B50" s="3" t="s">
         <v>23</v>
       </c>
@@ -12163,20 +11968,9 @@
       <c r="I50" s="14"/>
       <c r="J50" s="16"/>
       <c r="K50" s="14"/>
-      <c r="O50" s="38"/>
-      <c r="P50" s="38"/>
-      <c r="Q50" s="38"/>
-      <c r="R50" s="38"/>
-      <c r="S50" s="38"/>
-      <c r="T50" s="38"/>
-      <c r="U50" s="38"/>
-      <c r="V50" s="38"/>
-      <c r="W50" s="38"/>
-      <c r="X50" s="38"/>
-      <c r="Y50" s="38"/>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A51" s="28"/>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A51" s="45"/>
       <c r="B51" s="3" t="s">
         <v>24</v>
       </c>
@@ -12196,18 +11990,18 @@
       <c r="J51" s="16"/>
       <c r="K51" s="14"/>
     </row>
-    <row r="52" spans="1:25" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A52" s="28"/>
+    <row r="52" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A52" s="45"/>
       <c r="B52" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C52" s="18"/>
       <c r="D52" s="20"/>
       <c r="E52" s="20"/>
-      <c r="F52" s="45">
+      <c r="F52" s="36">
         <v>37.31</v>
       </c>
-      <c r="G52" s="45">
+      <c r="G52" s="36">
         <v>215.42</v>
       </c>
       <c r="H52" s="20"/>
@@ -12215,8 +12009,8 @@
       <c r="J52" s="16"/>
       <c r="K52" s="14"/>
     </row>
-    <row r="53" spans="1:25" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A53" s="27" t="s">
+    <row r="53" spans="1:13" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A53" s="44" t="s">
         <v>14</v>
       </c>
       <c r="B53" s="1" t="s">
@@ -12236,8 +12030,8 @@
       <c r="J53" s="13"/>
       <c r="K53" s="12"/>
     </row>
-    <row r="54" spans="1:25" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A54" s="28"/>
+    <row r="54" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A54" s="45"/>
       <c r="B54" s="3" t="s">
         <v>22</v>
       </c>
@@ -12261,8 +12055,8 @@
       <c r="J54" s="16"/>
       <c r="K54" s="14"/>
     </row>
-    <row r="55" spans="1:25" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A55" s="28"/>
+    <row r="55" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A55" s="45"/>
       <c r="B55" s="3" t="s">
         <v>23</v>
       </c>
@@ -12277,10 +12071,10 @@
       <c r="I55" s="14"/>
       <c r="J55" s="16"/>
       <c r="K55" s="14"/>
-      <c r="M55" s="40"/>
+      <c r="M55" s="31"/>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A56" s="28"/>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A56" s="45"/>
       <c r="B56" s="3" t="s">
         <v>24</v>
       </c>
@@ -12300,27 +12094,27 @@
       <c r="J56" s="16"/>
       <c r="K56" s="14"/>
     </row>
-    <row r="57" spans="1:25" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A57" s="28"/>
+    <row r="57" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A57" s="45"/>
       <c r="B57" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C57" s="18"/>
       <c r="D57" s="20"/>
-      <c r="E57" s="46"/>
-      <c r="F57" s="45">
+      <c r="E57" s="37"/>
+      <c r="F57" s="36">
         <v>28.61</v>
       </c>
-      <c r="G57" s="45">
+      <c r="G57" s="36">
         <v>198.66</v>
       </c>
-      <c r="H57" s="46"/>
-      <c r="I57" s="45"/>
+      <c r="H57" s="37"/>
+      <c r="I57" s="36"/>
       <c r="J57" s="16"/>
       <c r="K57" s="14"/>
     </row>
-    <row r="58" spans="1:25" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A58" s="27" t="s">
+    <row r="58" spans="1:13" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="44" t="s">
         <v>15</v>
       </c>
       <c r="B58" s="1" t="s">
@@ -12340,8 +12134,8 @@
       <c r="J58" s="16"/>
       <c r="K58" s="14"/>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A59" s="28"/>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A59" s="45"/>
       <c r="B59" s="3" t="s">
         <v>22</v>
       </c>
@@ -12365,8 +12159,8 @@
       <c r="J59" s="16"/>
       <c r="K59" s="14"/>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A60" s="28"/>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A60" s="45"/>
       <c r="B60" s="3" t="s">
         <v>23</v>
       </c>
@@ -12382,8 +12176,8 @@
       <c r="J60" s="16"/>
       <c r="K60" s="14"/>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A61" s="28"/>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A61" s="45"/>
       <c r="B61" s="3" t="s">
         <v>24</v>
       </c>
@@ -12403,33 +12197,33 @@
       <c r="J61" s="16"/>
       <c r="K61" s="14"/>
     </row>
-    <row r="62" spans="1:25" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A62" s="28"/>
+    <row r="62" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A62" s="45"/>
       <c r="B62" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="18"/>
-      <c r="D62" s="46"/>
-      <c r="E62" s="47"/>
-      <c r="F62" s="45">
+      <c r="D62" s="37"/>
+      <c r="E62" s="38"/>
+      <c r="F62" s="36">
         <v>93.73</v>
       </c>
-      <c r="G62" s="45">
+      <c r="G62" s="36">
         <v>238.53</v>
       </c>
-      <c r="H62" s="46"/>
-      <c r="I62" s="45"/>
+      <c r="H62" s="37"/>
+      <c r="I62" s="36"/>
       <c r="J62" s="16"/>
       <c r="K62" s="14"/>
     </row>
-    <row r="63" spans="1:25" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A63" s="27" t="s">
+    <row r="63" spans="1:13" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="44" t="s">
         <v>67</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C63" s="49"/>
+      <c r="C63" s="40"/>
       <c r="D63" s="20"/>
       <c r="E63" s="14">
         <v>67.010000000000005</v>
@@ -12443,8 +12237,8 @@
       <c r="J63" s="12"/>
       <c r="K63" s="12"/>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A64" s="28"/>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A64" s="45"/>
       <c r="B64" s="3" t="s">
         <v>22</v>
       </c>
@@ -12452,25 +12246,25 @@
         <v>23.26</v>
       </c>
       <c r="D64" s="15">
-        <v>45.54</v>
+        <v>45.6</v>
       </c>
       <c r="E64" s="14">
-        <v>101.44</v>
-      </c>
-      <c r="F64" s="36"/>
+        <v>101.7</v>
+      </c>
+      <c r="F64" s="29">
+        <v>88.13</v>
+      </c>
       <c r="G64" s="20"/>
-      <c r="H64" s="36">
-        <v>123.71</v>
-      </c>
+      <c r="H64" s="29"/>
       <c r="I64" s="14"/>
       <c r="J64" s="15"/>
       <c r="K64" s="14"/>
-      <c r="M64" s="39" t="s">
+      <c r="M64" s="30" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A65" s="28"/>
+      <c r="A65" s="45"/>
       <c r="B65" s="3" t="s">
         <v>23</v>
       </c>
@@ -12479,64 +12273,70 @@
       <c r="E65" s="20"/>
       <c r="F65" s="24"/>
       <c r="G65" s="20"/>
-      <c r="H65" s="36"/>
+      <c r="H65" s="29"/>
       <c r="I65" s="14"/>
       <c r="J65" s="15"/>
       <c r="K65" s="14"/>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A66" s="28"/>
+      <c r="A66" s="45"/>
       <c r="B66" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="26"/>
       <c r="D66" s="20"/>
       <c r="E66" s="20"/>
-      <c r="F66" s="36"/>
-      <c r="G66" s="36"/>
+      <c r="F66" s="29">
+        <v>74.819999999999993</v>
+      </c>
+      <c r="G66" s="29">
+        <v>115.68</v>
+      </c>
       <c r="H66" s="20"/>
       <c r="I66" s="14">
-        <v>54.58</v>
+        <v>53.41</v>
       </c>
       <c r="J66" s="15"/>
       <c r="K66" s="14"/>
     </row>
     <row r="67" spans="1:20" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A67" s="30"/>
+      <c r="A67" s="46"/>
       <c r="B67" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C67" s="50"/>
-      <c r="D67" s="46"/>
-      <c r="E67" s="46"/>
-      <c r="F67" s="45">
+      <c r="C67" s="41"/>
+      <c r="D67" s="37"/>
+      <c r="E67" s="37"/>
+      <c r="F67" s="36">
         <v>24.67</v>
       </c>
-      <c r="G67" s="51"/>
-      <c r="H67" s="46"/>
-      <c r="I67" s="45"/>
-      <c r="J67" s="48"/>
-      <c r="K67" s="45"/>
+      <c r="G67" s="42">
+        <v>202.98</v>
+      </c>
+      <c r="H67" s="37"/>
+      <c r="I67" s="36"/>
+      <c r="J67" s="39"/>
+      <c r="K67" s="36"/>
     </row>
     <row r="68" spans="1:20" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
     <row r="69" spans="1:20" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="70" spans="1:20" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A70" s="31" t="s">
+      <c r="A70" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="B70" s="32"/>
-      <c r="C70" s="32"/>
-      <c r="D70" s="32"/>
-      <c r="E70" s="32"/>
-      <c r="F70" s="32"/>
-      <c r="G70" s="32"/>
-      <c r="H70" s="32"/>
-      <c r="I70" s="32"/>
-      <c r="J70" s="32"/>
-      <c r="K70" s="32"/>
-      <c r="L70" s="32"/>
-      <c r="M70" s="32"/>
-      <c r="N70" s="33"/>
+      <c r="B70" s="49"/>
+      <c r="C70" s="49"/>
+      <c r="D70" s="49"/>
+      <c r="E70" s="49"/>
+      <c r="F70" s="49"/>
+      <c r="G70" s="49"/>
+      <c r="H70" s="49"/>
+      <c r="I70" s="49"/>
+      <c r="J70" s="49"/>
+      <c r="K70" s="49"/>
+      <c r="L70" s="49"/>
+      <c r="M70" s="49"/>
+      <c r="N70" s="50"/>
     </row>
     <row r="71" spans="1:20" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A71" s="8"/>
@@ -12585,7 +12385,7 @@
       </c>
     </row>
     <row r="72" spans="1:20" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A72" s="27" t="s">
+      <c r="A72" s="44" t="s">
         <v>9</v>
       </c>
       <c r="B72" s="1" t="s">
@@ -12629,7 +12429,7 @@
       <c r="T72" s="2"/>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A73" s="28"/>
+      <c r="A73" s="45"/>
       <c r="B73" s="3" t="s">
         <v>19</v>
       </c>
@@ -12679,7 +12479,7 @@
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A74" s="28"/>
+      <c r="A74" s="45"/>
       <c r="B74" s="3" t="s">
         <v>20</v>
       </c>
@@ -12720,7 +12520,7 @@
       <c r="S74" s="7"/>
     </row>
     <row r="75" spans="1:20" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A75" s="30"/>
+      <c r="A75" s="46"/>
       <c r="B75" s="4" t="s">
         <v>26</v>
       </c>
@@ -12762,7 +12562,7 @@
       <c r="T75" s="5"/>
     </row>
     <row r="76" spans="1:20" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A76" s="27" t="s">
+      <c r="A76" s="44" t="s">
         <v>10</v>
       </c>
       <c r="B76" s="1" t="s">
@@ -12806,7 +12606,7 @@
       <c r="T76" s="2"/>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A77" s="28"/>
+      <c r="A77" s="45"/>
       <c r="B77" s="3" t="s">
         <v>19</v>
       </c>
@@ -12847,7 +12647,7 @@
       <c r="S77" s="7"/>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A78" s="28"/>
+      <c r="A78" s="45"/>
       <c r="B78" s="3" t="s">
         <v>20</v>
       </c>
@@ -12888,7 +12688,7 @@
       <c r="S78" s="7"/>
     </row>
     <row r="79" spans="1:20" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A79" s="30"/>
+      <c r="A79" s="46"/>
       <c r="B79" s="4" t="s">
         <v>26</v>
       </c>
@@ -12930,7 +12730,7 @@
       <c r="T79" s="5"/>
     </row>
     <row r="80" spans="1:20" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A80" s="28" t="s">
+      <c r="A80" s="45" t="s">
         <v>11</v>
       </c>
       <c r="B80" s="1" t="s">
@@ -12974,7 +12774,7 @@
       <c r="T80" s="2"/>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A81" s="28"/>
+      <c r="A81" s="45"/>
       <c r="B81" s="3" t="s">
         <v>19</v>
       </c>
@@ -13015,7 +12815,7 @@
       <c r="S81" s="7"/>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A82" s="28"/>
+      <c r="A82" s="45"/>
       <c r="B82" s="3" t="s">
         <v>20</v>
       </c>
@@ -13056,7 +12856,7 @@
       <c r="S82" s="7"/>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A83" s="28"/>
+      <c r="A83" s="45"/>
       <c r="B83" s="3" t="s">
         <v>29</v>
       </c>
@@ -13097,7 +12897,7 @@
       <c r="S83" s="7"/>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A84" s="28"/>
+      <c r="A84" s="45"/>
       <c r="B84" s="3" t="s">
         <v>30</v>
       </c>
@@ -13138,7 +12938,7 @@
       <c r="S84" s="7"/>
     </row>
     <row r="85" spans="1:20" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A85" s="30"/>
+      <c r="A85" s="46"/>
       <c r="B85" s="4" t="s">
         <v>26</v>
       </c>
@@ -13180,7 +12980,7 @@
       <c r="T85" s="5"/>
     </row>
     <row r="86" spans="1:20" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A86" s="27" t="s">
+      <c r="A86" s="44" t="s">
         <v>12</v>
       </c>
       <c r="B86" s="1" t="s">
@@ -13224,7 +13024,7 @@
       <c r="T86" s="2"/>
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A87" s="28"/>
+      <c r="A87" s="45"/>
       <c r="B87" s="3" t="s">
         <v>19</v>
       </c>
@@ -13274,7 +13074,7 @@
       </c>
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A88" s="28"/>
+      <c r="A88" s="45"/>
       <c r="B88" s="3" t="s">
         <v>20</v>
       </c>
@@ -13315,7 +13115,7 @@
       <c r="S88" s="7"/>
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A89" s="28"/>
+      <c r="A89" s="45"/>
       <c r="B89" s="3" t="s">
         <v>29</v>
       </c>
@@ -13356,7 +13156,7 @@
       <c r="S89" s="7"/>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A90" s="28"/>
+      <c r="A90" s="45"/>
       <c r="B90" s="3" t="s">
         <v>30</v>
       </c>
@@ -13397,7 +13197,7 @@
       <c r="S90" s="7"/>
     </row>
     <row r="91" spans="1:20" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A91" s="30"/>
+      <c r="A91" s="46"/>
       <c r="B91" s="4" t="s">
         <v>26</v>
       </c>
@@ -13439,7 +13239,7 @@
       <c r="T91" s="5"/>
     </row>
     <row r="92" spans="1:20" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A92" s="27" t="s">
+      <c r="A92" s="44" t="s">
         <v>13</v>
       </c>
       <c r="B92" s="1" t="s">
@@ -13483,7 +13283,7 @@
       <c r="T92" s="2"/>
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A93" s="28"/>
+      <c r="A93" s="45"/>
       <c r="B93" s="3" t="s">
         <v>19</v>
       </c>
@@ -13524,7 +13324,7 @@
       <c r="S93" s="7"/>
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A94" s="28"/>
+      <c r="A94" s="45"/>
       <c r="B94" s="3" t="s">
         <v>20</v>
       </c>
@@ -13565,7 +13365,7 @@
       <c r="S94" s="7"/>
     </row>
     <row r="95" spans="1:20" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A95" s="30"/>
+      <c r="A95" s="46"/>
       <c r="B95" s="4" t="s">
         <v>26</v>
       </c>
@@ -13607,7 +13407,7 @@
       <c r="T95" s="5"/>
     </row>
     <row r="96" spans="1:20" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A96" s="27" t="s">
+      <c r="A96" s="44" t="s">
         <v>14</v>
       </c>
       <c r="B96" s="1" t="s">
@@ -13651,7 +13451,7 @@
       <c r="T96" s="2"/>
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A97" s="28"/>
+      <c r="A97" s="45"/>
       <c r="B97" s="3" t="s">
         <v>19</v>
       </c>
@@ -13701,7 +13501,7 @@
       </c>
     </row>
     <row r="98" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A98" s="28"/>
+      <c r="A98" s="45"/>
       <c r="B98" s="3" t="s">
         <v>20</v>
       </c>
@@ -13742,7 +13542,7 @@
       <c r="S98" s="7"/>
     </row>
     <row r="99" spans="1:20" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A99" s="30"/>
+      <c r="A99" s="46"/>
       <c r="B99" s="4" t="s">
         <v>26</v>
       </c>
@@ -13784,7 +13584,7 @@
       <c r="T99" s="5"/>
     </row>
     <row r="100" spans="1:20" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A100" s="27" t="s">
+      <c r="A100" s="44" t="s">
         <v>15</v>
       </c>
       <c r="B100" s="1" t="s">
@@ -13827,7 +13627,7 @@
       <c r="S100" s="7"/>
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A101" s="28"/>
+      <c r="A101" s="45"/>
       <c r="B101" s="3" t="s">
         <v>19</v>
       </c>
@@ -13868,7 +13668,7 @@
       <c r="S101" s="7"/>
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A102" s="28"/>
+      <c r="A102" s="45"/>
       <c r="B102" s="3" t="s">
         <v>20</v>
       </c>
@@ -13909,7 +13709,7 @@
       <c r="S102" s="7"/>
     </row>
     <row r="103" spans="1:20" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A103" s="30"/>
+      <c r="A103" s="46"/>
       <c r="B103" s="4" t="s">
         <v>26</v>
       </c>
@@ -13953,20 +13753,11 @@
     <row r="104" spans="1:20" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A43:A47"/>
-    <mergeCell ref="N43:N44"/>
-    <mergeCell ref="N45:N46"/>
-    <mergeCell ref="N22:N23"/>
-    <mergeCell ref="N24:N25"/>
-    <mergeCell ref="N26:N27"/>
-    <mergeCell ref="N28:N29"/>
-    <mergeCell ref="N41:N42"/>
-    <mergeCell ref="N20:N21"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A28:A32"/>
     <mergeCell ref="A33:A37"/>
     <mergeCell ref="A38:A42"/>
-    <mergeCell ref="A92:A95"/>
+    <mergeCell ref="A43:A47"/>
     <mergeCell ref="A96:A99"/>
     <mergeCell ref="A100:A103"/>
     <mergeCell ref="A13:G13"/>
@@ -13981,25 +13772,34 @@
     <mergeCell ref="A70:N70"/>
     <mergeCell ref="N16:N17"/>
     <mergeCell ref="N18:N19"/>
-    <mergeCell ref="R22:R24"/>
-    <mergeCell ref="R25:R27"/>
-    <mergeCell ref="R28:R30"/>
+    <mergeCell ref="N20:N21"/>
+    <mergeCell ref="N43:N44"/>
     <mergeCell ref="A63:A67"/>
     <mergeCell ref="N47:N48"/>
+    <mergeCell ref="N37:N38"/>
+    <mergeCell ref="N39:N40"/>
+    <mergeCell ref="A92:A95"/>
+    <mergeCell ref="N45:N46"/>
+    <mergeCell ref="N41:N42"/>
+    <mergeCell ref="N35:N36"/>
     <mergeCell ref="V16:V18"/>
     <mergeCell ref="V19:V21"/>
     <mergeCell ref="V22:V24"/>
     <mergeCell ref="V25:V27"/>
     <mergeCell ref="V28:V30"/>
+    <mergeCell ref="R22:R24"/>
+    <mergeCell ref="R25:R27"/>
+    <mergeCell ref="R28:R30"/>
+    <mergeCell ref="N22:N23"/>
+    <mergeCell ref="N24:N25"/>
+    <mergeCell ref="N26:N27"/>
+    <mergeCell ref="N28:N29"/>
+    <mergeCell ref="R16:R18"/>
+    <mergeCell ref="R19:R21"/>
     <mergeCell ref="V31:V33"/>
     <mergeCell ref="V34:V36"/>
     <mergeCell ref="R31:R33"/>
     <mergeCell ref="R34:R36"/>
-    <mergeCell ref="N35:N36"/>
-    <mergeCell ref="N37:N38"/>
-    <mergeCell ref="N39:N40"/>
-    <mergeCell ref="R16:R18"/>
-    <mergeCell ref="R19:R21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/AlgorithmNData/Bug Algorithms Full Documented Values.xlsx
+++ b/AlgorithmNData/Bug Algorithms Full Documented Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utrgv-my.sharepoint.com/personal/izabella_valero01_utrgv_edu/Documents/Desktop/MARS Research/May20-PathPlanning/webots/mars-github-bug-algorithms/bug_algorithms/AlgorithmNData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1214" documentId="8_{3A44FF85-21B8-4464-9902-83D39A64E269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A08C817-3DB1-4618-B7F1-3433423008CB}"/>
+  <xr:revisionPtr revIDLastSave="1331" documentId="8_{3A44FF85-21B8-4464-9902-83D39A64E269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4DA8FE5-48E3-4466-B7C3-36E473EFD208}"/>
   <bookViews>
-    <workbookView xWindow="7973" yWindow="15" windowWidth="14527" windowHeight="11115" xr2:uid="{1B981E3A-1744-4B50-BA68-B582BA61DD63}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="11415" windowHeight="14362" xr2:uid="{1B981E3A-1744-4B50-BA68-B582BA61DD63}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <definedName name="we">Sheet1!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="72">
   <si>
     <t>basic_block</t>
   </si>
@@ -248,6 +247,15 @@
   </si>
   <si>
     <t>note: the algorithm does not seem to perform properly on the more complex maps. Will evaluate and determine if the algorithm has a bug or performs poorly on the map.</t>
+  </si>
+  <si>
+    <t>AltBug</t>
+  </si>
+  <si>
+    <t>Vertival-ROGO</t>
+  </si>
+  <si>
+    <t>AltComboBug</t>
   </si>
 </sst>
 </file>
@@ -513,7 +521,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -588,7 +596,7 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -597,9 +605,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -611,6 +616,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -712,17 +728,6 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$O$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Basic Block</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -735,9 +740,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$N$6:$N$12</c:f>
+              <c:f>Sheet1!$N$6:$N$13</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>Bug0</c:v>
                 </c:pt>
@@ -758,16 +763,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>ComboBug</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>AltBug</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$O$6:$O$12</c:f>
+              <c:f>Sheet1!$O$6:$O$13</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>24.19</c:v>
                 </c:pt>
@@ -788,11 +796,29 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>22.85</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>23.26</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredSeriesTitle>
+                <c15:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref> </c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                  </c:strRef>
+                </c15:tx>
+              </c15:filteredSeriesTitle>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-407F-4383-8CC2-1969B17BB217}"/>
             </c:ext>
@@ -1049,17 +1075,6 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$S$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Double_Block</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -1072,9 +1087,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$R$6:$R$12</c:f>
+              <c:f>Sheet1!$R$6:$R$13</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>Bug0</c:v>
                 </c:pt>
@@ -1095,16 +1110,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>ComboBug</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>AltBug</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$S$6:$S$12</c:f>
+              <c:f>Sheet1!$S$6:$S$13</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>41.57</c:v>
                 </c:pt>
@@ -1125,11 +1143,29 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>37.86</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredSeriesTitle>
+                <c15:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref> </c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                  </c:strRef>
+                </c15:tx>
+              </c15:filteredSeriesTitle>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-6838-4005-B0E8-D354D16495A6}"/>
             </c:ext>
@@ -1353,17 +1389,6 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$P$15</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>C Trap</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -1376,9 +1401,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$N$16:$O$29</c:f>
+              <c:f>Sheet1!$N$16:$O$31</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="16"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>Horizontal-ROGO</c:v>
@@ -1422,6 +1447,12 @@
                   <c:pt idx="13">
                     <c:v>Vertical-ROGO</c:v>
                   </c:pt>
+                  <c:pt idx="14">
+                    <c:v>Horizontal-ROGO</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>Vertical-ROGO</c:v>
+                  </c:pt>
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
@@ -1445,16 +1476,19 @@
                   <c:pt idx="12">
                     <c:v>ComboBug</c:v>
                   </c:pt>
+                  <c:pt idx="14">
+                    <c:v>AltBug</c:v>
+                  </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
             </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$P$16:$P$29</c:f>
+              <c:f>Sheet1!$P$16:$P$31</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>72.77</c:v>
                 </c:pt>
@@ -1496,11 +1530,32 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>40.51</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>67.010000000000005</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>101.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredSeriesTitle>
+                <c15:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref> </c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                  </c:strRef>
+                </c15:tx>
+              </c15:filteredSeriesTitle>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-857B-41C9-ABBE-CA7823C152EA}"/>
             </c:ext>
@@ -1684,36 +1739,6 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
@@ -1724,17 +1749,6 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$T$15</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Box Spiral</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -1747,9 +1761,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$R$16:$S$36</c:f>
+              <c:f>Sheet1!$R$16:$S$39</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="24"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>Vertical-ROGO</c:v>
@@ -1814,6 +1828,15 @@
                   <c:pt idx="20">
                     <c:v>Vertical-ROGI</c:v>
                   </c:pt>
+                  <c:pt idx="21">
+                    <c:v>Vertival-ROGO</c:v>
+                  </c:pt>
+                  <c:pt idx="22">
+                    <c:v>Horizontal-ROGI</c:v>
+                  </c:pt>
+                  <c:pt idx="23">
+                    <c:v>Horizontal-ROGI</c:v>
+                  </c:pt>
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
@@ -1837,16 +1860,19 @@
                   <c:pt idx="18">
                     <c:v>ComboBug</c:v>
                   </c:pt>
+                  <c:pt idx="21">
+                    <c:v>AltBug</c:v>
+                  </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
             </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$T$16:$T$36</c:f>
+              <c:f>Sheet1!$T$16:$T$39</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>36.29</c:v>
                 </c:pt>
@@ -1909,11 +1935,35 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>93.73</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>88.13</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>74.819999999999993</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24.67</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredSeriesTitle>
+                <c15:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref> </c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                  </c:strRef>
+                </c15:tx>
+              </c15:filteredSeriesTitle>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-D0F4-49EA-B57E-4E933492F0F5}"/>
             </c:ext>
@@ -2097,36 +2147,6 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
@@ -2137,17 +2157,6 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$P$34</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Double Spiral</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -2160,9 +2169,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$N$35:$O$48</c:f>
+              <c:f>Sheet1!$N$35:$O$50</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="16"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>Horizontal-ROGI</c:v>
@@ -2206,6 +2215,12 @@
                   <c:pt idx="13">
                     <c:v>Vertical-ROGI</c:v>
                   </c:pt>
+                  <c:pt idx="14">
+                    <c:v>Horizontal-ROGI</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>Vertical-ROGI</c:v>
+                  </c:pt>
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
@@ -2229,16 +2244,19 @@
                   <c:pt idx="12">
                     <c:v>ComboBug</c:v>
                   </c:pt>
+                  <c:pt idx="14">
+                    <c:v>AltBug</c:v>
+                  </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
             </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$P$35:$P$48</c:f>
+              <c:f>Sheet1!$P$35:$P$50</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>155.71</c:v>
                 </c:pt>
@@ -2280,11 +2298,32 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>238.53</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>115.68</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>202.98</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredSeriesTitle>
+                <c15:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref> </c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                  </c:strRef>
+                </c15:tx>
+              </c15:filteredSeriesTitle>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-17A4-4C96-9B01-714466C4924F}"/>
             </c:ext>
@@ -2508,17 +2547,6 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$X$15</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Short Maze</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -2531,9 +2559,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$V$16:$W$36</c:f>
+              <c:f>Sheet1!$V$16:$W$39</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="24"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>Horizontal-ROGO</c:v>
@@ -2598,6 +2626,15 @@
                   <c:pt idx="20">
                     <c:v>Diagonal-ROGO</c:v>
                   </c:pt>
+                  <c:pt idx="21">
+                    <c:v>Horizontal-ROGO</c:v>
+                  </c:pt>
+                  <c:pt idx="22">
+                    <c:v>Vertical-ROGO</c:v>
+                  </c:pt>
+                  <c:pt idx="23">
+                    <c:v>Diagonal-ROGO</c:v>
+                  </c:pt>
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
@@ -2621,16 +2658,19 @@
                   <c:pt idx="18">
                     <c:v>ComboBug</c:v>
                   </c:pt>
+                  <c:pt idx="21">
+                    <c:v>AltBug</c:v>
+                  </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
             </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$X$16:$X$36</c:f>
+              <c:f>Sheet1!$X$16:$X$39</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>95.23</c:v>
                 </c:pt>
@@ -2693,11 +2733,29 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>82.3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>68.61</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredSeriesTitle>
+                <c15:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref> </c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                  </c:strRef>
+                </c15:tx>
+              </c15:filteredSeriesTitle>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-A5E1-4B48-8629-D29779254037}"/>
             </c:ext>
@@ -2946,17 +3004,6 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$T$40</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Trap Maze</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -2969,9 +3016,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$41:$S$47</c:f>
+              <c:f>Sheet1!$S$41:$S$48</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>Bug0</c:v>
                 </c:pt>
@@ -2992,16 +3039,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>ComboBug</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>AltBug</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$T$41:$T$47</c:f>
+              <c:f>Sheet1!$T$41:$T$48</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>209.79</c:v>
                 </c:pt>
@@ -3022,11 +3072,29 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>206.27</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>53.41</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredSeriesTitle>
+                <c15:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref> </c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                  </c:strRef>
+                </c15:tx>
+              </c15:filteredSeriesTitle>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-3DD6-4CAD-8D76-C18E502EBE4A}"/>
             </c:ext>
@@ -3280,17 +3348,6 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$AP$12</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Bug0</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -3397,6 +3454,21 @@
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredSeriesTitle>
+                <c15:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref> </c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                  </c:strRef>
+                </c15:tx>
+              </c15:filteredSeriesTitle>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-260B-4B28-BA19-EE3DFE33E5A7}"/>
             </c:ext>
@@ -3405,17 +3477,6 @@
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$AP$13</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Bug2</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent2"/>
@@ -3522,6 +3583,21 @@
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredSeriesTitle>
+                <c15:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref> </c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                  </c:strRef>
+                </c15:tx>
+              </c15:filteredSeriesTitle>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-260B-4B28-BA19-EE3DFE33E5A7}"/>
             </c:ext>
@@ -3530,17 +3606,6 @@
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$AP$14</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Alg1</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent3"/>
@@ -3647,6 +3712,21 @@
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredSeriesTitle>
+                <c15:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref> </c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                  </c:strRef>
+                </c15:tx>
+              </c15:filteredSeriesTitle>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-260B-4B28-BA19-EE3DFE33E5A7}"/>
             </c:ext>
@@ -3655,17 +3735,6 @@
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$AP$15</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Alg2</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent4"/>
@@ -3772,6 +3841,21 @@
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredSeriesTitle>
+                <c15:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref> </c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                  </c:strRef>
+                </c15:tx>
+              </c15:filteredSeriesTitle>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-260B-4B28-BA19-EE3DFE33E5A7}"/>
             </c:ext>
@@ -3780,17 +3864,6 @@
         <c:ser>
           <c:idx val="4"/>
           <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$AP$16</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Rev1</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent5"/>
@@ -3897,6 +3970,21 @@
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredSeriesTitle>
+                <c15:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref> </c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                  </c:strRef>
+                </c15:tx>
+              </c15:filteredSeriesTitle>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000004-260B-4B28-BA19-EE3DFE33E5A7}"/>
             </c:ext>
@@ -3905,17 +3993,6 @@
         <c:ser>
           <c:idx val="5"/>
           <c:order val="5"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$AP$17</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Rev2</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent6"/>
@@ -4022,6 +4099,21 @@
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredSeriesTitle>
+                <c15:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref> </c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                  </c:strRef>
+                </c15:tx>
+              </c15:filteredSeriesTitle>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-260B-4B28-BA19-EE3DFE33E5A7}"/>
             </c:ext>
@@ -4030,17 +4122,6 @@
         <c:ser>
           <c:idx val="6"/>
           <c:order val="6"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$AP$18</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ComboBug</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent1">
@@ -4149,6 +4230,21 @@
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredSeriesTitle>
+                <c15:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref> </c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                  </c:strRef>
+                </c15:tx>
+              </c15:filteredSeriesTitle>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-260B-4B28-BA19-EE3DFE33E5A7}"/>
             </c:ext>
@@ -10249,19 +10345,32 @@
   <cols>
     <col min="1" max="13" width="16.59765625" customWidth="1"/>
     <col min="14" max="15" width="16.53125" customWidth="1"/>
+    <col min="41" max="41" width="6.9296875" customWidth="1"/>
+    <col min="42" max="42" width="14.19921875" customWidth="1"/>
+    <col min="43" max="43" width="10.1328125" customWidth="1"/>
+    <col min="44" max="44" width="13.796875" customWidth="1"/>
+    <col min="45" max="45" width="13.19921875" customWidth="1"/>
+    <col min="46" max="46" width="12.53125" customWidth="1"/>
+    <col min="47" max="47" width="15.33203125" customWidth="1"/>
+    <col min="48" max="48" width="14.6640625" customWidth="1"/>
+    <col min="49" max="49" width="14.53125" customWidth="1"/>
+    <col min="50" max="50" width="17.265625" customWidth="1"/>
+    <col min="51" max="51" width="17.9296875" customWidth="1"/>
+    <col min="52" max="52" width="16" customWidth="1"/>
+    <col min="53" max="54" width="15.9296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:62" x14ac:dyDescent="0.45">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="A3" s="43"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
     </row>
     <row r="4" spans="1:62" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="5" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -10341,6 +10450,7 @@
       <c r="S10" s="15">
         <v>62.37</v>
       </c>
+      <c r="AQ10" s="5"/>
     </row>
     <row r="11" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N11" t="s">
@@ -10355,7 +10465,8 @@
       <c r="S11" s="15">
         <v>44.92</v>
       </c>
-      <c r="AQ11" t="s">
+      <c r="AP11" s="9"/>
+      <c r="AQ11" s="9" t="s">
         <v>42</v>
       </c>
       <c r="AR11" s="10" t="s">
@@ -10408,7 +10519,7 @@
       <c r="S12" s="15">
         <v>37.86</v>
       </c>
-      <c r="AP12" t="s">
+      <c r="AP12" s="9" t="s">
         <v>35</v>
       </c>
       <c r="AQ12" s="14">
@@ -10452,15 +10563,26 @@
       </c>
     </row>
     <row r="13" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="47"/>
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="O13" s="14"/>
-      <c r="AP13" t="s">
+      <c r="A13" s="43"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="N13" t="s">
+        <v>69</v>
+      </c>
+      <c r="O13" s="14">
+        <v>23.26</v>
+      </c>
+      <c r="R13" t="s">
+        <v>69</v>
+      </c>
+      <c r="S13" s="53">
+        <v>45.6</v>
+      </c>
+      <c r="AP13" s="9" t="s">
         <v>36</v>
       </c>
       <c r="AQ13" s="14">
@@ -10469,7 +10591,7 @@
       <c r="AR13" s="15">
         <v>60.93</v>
       </c>
-      <c r="AS13" s="12">
+      <c r="AS13" s="14">
         <v>75.84</v>
       </c>
       <c r="AT13" s="14">
@@ -10490,10 +10612,10 @@
       <c r="AY13" s="14">
         <v>272.77</v>
       </c>
-      <c r="AZ13" s="12">
+      <c r="AZ13" s="14">
         <v>111.42</v>
       </c>
-      <c r="BA13" s="14">
+      <c r="BA13" s="28">
         <v>94.18</v>
       </c>
       <c r="BB13" s="14">
@@ -10504,7 +10626,7 @@
       </c>
     </row>
     <row r="14" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="AP14" t="s">
+      <c r="AP14" s="6" t="s">
         <v>37</v>
       </c>
       <c r="AQ14" s="14">
@@ -10513,7 +10635,7 @@
       <c r="AR14" s="15">
         <v>60.93</v>
       </c>
-      <c r="AS14" s="12">
+      <c r="AS14" s="14">
         <v>75.84</v>
       </c>
       <c r="AT14" s="14">
@@ -10534,10 +10656,10 @@
       <c r="AY14" s="14">
         <v>301.92</v>
       </c>
-      <c r="AZ14" s="12">
+      <c r="AZ14" s="14">
         <v>111.42</v>
       </c>
-      <c r="BA14" s="14">
+      <c r="BA14" s="28">
         <v>94.18</v>
       </c>
       <c r="BB14" s="14">
@@ -10557,7 +10679,7 @@
       <c r="X15" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="AP15" t="s">
+      <c r="AP15" s="9" t="s">
         <v>38</v>
       </c>
       <c r="AQ15" s="14">
@@ -10566,7 +10688,7 @@
       <c r="AR15" s="15">
         <v>41.95</v>
       </c>
-      <c r="AS15" s="12">
+      <c r="AS15" s="14">
         <v>72.77</v>
       </c>
       <c r="AT15" s="14">
@@ -10587,10 +10709,10 @@
       <c r="AY15" s="14">
         <v>282.66000000000003</v>
       </c>
-      <c r="AZ15" s="12">
+      <c r="AZ15" s="14">
         <v>96.06</v>
       </c>
-      <c r="BA15" s="14">
+      <c r="BA15" s="28">
         <v>66.400000000000006</v>
       </c>
       <c r="BB15" s="14">
@@ -10607,7 +10729,7 @@
       </c>
     </row>
     <row r="16" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="N16" s="43" t="s">
+      <c r="N16" s="50" t="s">
         <v>35</v>
       </c>
       <c r="O16" s="1" t="s">
@@ -10616,7 +10738,7 @@
       <c r="P16" s="12">
         <v>72.77</v>
       </c>
-      <c r="R16" s="43" t="s">
+      <c r="R16" s="50" t="s">
         <v>35</v>
       </c>
       <c r="S16" s="3" t="s">
@@ -10625,7 +10747,7 @@
       <c r="T16" s="14">
         <v>36.29</v>
       </c>
-      <c r="V16" s="43" t="s">
+      <c r="V16" s="50" t="s">
         <v>35</v>
       </c>
       <c r="W16" s="1" t="s">
@@ -10634,7 +10756,7 @@
       <c r="X16" s="12">
         <v>95.23</v>
       </c>
-      <c r="AP16" t="s">
+      <c r="AP16" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AQ16" s="14">
@@ -10643,7 +10765,7 @@
       <c r="AR16" s="15">
         <v>62.37</v>
       </c>
-      <c r="AS16" s="12">
+      <c r="AS16" s="14">
         <v>76.03</v>
       </c>
       <c r="AT16" s="14">
@@ -10664,10 +10786,10 @@
       <c r="AY16" s="14">
         <v>215.42</v>
       </c>
-      <c r="AZ16" s="12">
+      <c r="AZ16" s="14">
         <v>111.3</v>
       </c>
-      <c r="BA16" s="14">
+      <c r="BA16" s="28">
         <v>93.06</v>
       </c>
       <c r="BB16" s="14">
@@ -10684,28 +10806,28 @@
       </c>
     </row>
     <row r="17" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="N17" s="43"/>
+      <c r="N17" s="50"/>
       <c r="O17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="P17" s="14">
         <v>48.86</v>
       </c>
-      <c r="R17" s="43"/>
+      <c r="R17" s="50"/>
       <c r="S17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="T17" s="14">
         <v>77.44</v>
       </c>
-      <c r="V17" s="43"/>
+      <c r="V17" s="50"/>
       <c r="W17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="X17" s="14">
         <v>66.400000000000006</v>
       </c>
-      <c r="AP17" t="s">
+      <c r="AP17" s="6" t="s">
         <v>40</v>
       </c>
       <c r="AQ17" s="14">
@@ -10714,7 +10836,7 @@
       <c r="AR17" s="15">
         <v>44.92</v>
       </c>
-      <c r="AS17" s="12">
+      <c r="AS17" s="14">
         <v>67.260000000000005</v>
       </c>
       <c r="AT17" s="14">
@@ -10735,7 +10857,7 @@
       <c r="AY17" s="14">
         <v>198.66</v>
       </c>
-      <c r="AZ17" s="12">
+      <c r="AZ17" s="14">
         <v>68.67</v>
       </c>
       <c r="BA17" s="14">
@@ -10755,7 +10877,7 @@
       </c>
     </row>
     <row r="18" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="N18" s="43" t="s">
+      <c r="N18" s="50" t="s">
         <v>36</v>
       </c>
       <c r="O18" s="1" t="s">
@@ -10764,21 +10886,21 @@
       <c r="P18" s="12">
         <v>75.84</v>
       </c>
-      <c r="R18" s="43"/>
+      <c r="R18" s="50"/>
       <c r="S18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="T18" s="14">
         <v>96.03</v>
       </c>
-      <c r="V18" s="43"/>
+      <c r="V18" s="50"/>
       <c r="W18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="X18" s="14">
         <v>83.65</v>
       </c>
-      <c r="AP18" t="s">
+      <c r="AP18" s="6" t="s">
         <v>41</v>
       </c>
       <c r="AQ18" s="14">
@@ -10828,14 +10950,14 @@
       </c>
     </row>
     <row r="19" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="N19" s="43"/>
+      <c r="N19" s="50"/>
       <c r="O19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="P19" s="14">
         <v>64.19</v>
       </c>
-      <c r="R19" s="43" t="s">
+      <c r="R19" s="50" t="s">
         <v>36</v>
       </c>
       <c r="S19" s="3" t="s">
@@ -10844,7 +10966,7 @@
       <c r="T19" s="14">
         <v>56.54</v>
       </c>
-      <c r="V19" s="43" t="s">
+      <c r="V19" s="50" t="s">
         <v>36</v>
       </c>
       <c r="W19" s="1" t="s">
@@ -10853,6 +10975,44 @@
       <c r="X19" s="12">
         <v>111.42</v>
       </c>
+      <c r="AP19" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="AQ19" s="52">
+        <v>23.26</v>
+      </c>
+      <c r="AR19" s="53">
+        <v>45.6</v>
+      </c>
+      <c r="AS19" s="56">
+        <v>72.77</v>
+      </c>
+      <c r="AT19" s="56">
+        <v>48.86</v>
+      </c>
+      <c r="AU19" s="56">
+        <v>88.13</v>
+      </c>
+      <c r="AV19" s="56">
+        <v>74.819999999999993</v>
+      </c>
+      <c r="AW19" s="56">
+        <v>24.67</v>
+      </c>
+      <c r="AX19" s="56">
+        <v>115.68</v>
+      </c>
+      <c r="AY19" s="56">
+        <v>202.98</v>
+      </c>
+      <c r="AZ19" s="56">
+        <v>68.61</v>
+      </c>
+      <c r="BA19" s="5"/>
+      <c r="BB19" s="8"/>
+      <c r="BC19" s="56">
+        <v>53.41</v>
+      </c>
       <c r="BI19" s="9" t="s">
         <v>50</v>
       </c>
@@ -10861,7 +11021,7 @@
       </c>
     </row>
     <row r="20" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="N20" s="43" t="s">
+      <c r="N20" s="50" t="s">
         <v>37</v>
       </c>
       <c r="O20" s="1" t="s">
@@ -10870,20 +11030,22 @@
       <c r="P20" s="12">
         <v>75.84</v>
       </c>
-      <c r="R20" s="43"/>
+      <c r="R20" s="50"/>
       <c r="S20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="T20" s="14">
         <v>80.64</v>
       </c>
-      <c r="V20" s="43"/>
+      <c r="V20" s="50"/>
       <c r="W20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="X20" s="14">
         <v>94.18</v>
       </c>
+      <c r="AQ20" s="2"/>
+      <c r="AR20" s="2"/>
       <c r="BI20" s="9" t="s">
         <v>51</v>
       </c>
@@ -10892,21 +11054,21 @@
       </c>
     </row>
     <row r="21" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="N21" s="43"/>
+      <c r="N21" s="50"/>
       <c r="O21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="P21" s="14">
         <v>63.19</v>
       </c>
-      <c r="R21" s="43"/>
+      <c r="R21" s="50"/>
       <c r="S21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="T21" s="14">
         <v>121.95</v>
       </c>
-      <c r="V21" s="43"/>
+      <c r="V21" s="50"/>
       <c r="W21" s="3" t="s">
         <v>23</v>
       </c>
@@ -10921,7 +11083,7 @@
       </c>
     </row>
     <row r="22" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="N22" s="43" t="s">
+      <c r="N22" s="50" t="s">
         <v>38</v>
       </c>
       <c r="O22" s="1" t="s">
@@ -10930,7 +11092,7 @@
       <c r="P22" s="12">
         <v>72.77</v>
       </c>
-      <c r="R22" s="43" t="s">
+      <c r="R22" s="50" t="s">
         <v>37</v>
       </c>
       <c r="S22" s="3" t="s">
@@ -10939,7 +11101,7 @@
       <c r="T22" s="14">
         <v>56.54</v>
       </c>
-      <c r="V22" s="43" t="s">
+      <c r="V22" s="50" t="s">
         <v>37</v>
       </c>
       <c r="W22" s="1" t="s">
@@ -10956,21 +11118,21 @@
       </c>
     </row>
     <row r="23" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="N23" s="43"/>
+      <c r="N23" s="50"/>
       <c r="O23" s="3" t="s">
         <v>22</v>
       </c>
       <c r="P23" s="14">
         <v>48.86</v>
       </c>
-      <c r="R23" s="43"/>
+      <c r="R23" s="50"/>
       <c r="S23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="T23" s="14">
         <v>82.53</v>
       </c>
-      <c r="V23" s="43"/>
+      <c r="V23" s="50"/>
       <c r="W23" s="3" t="s">
         <v>22</v>
       </c>
@@ -10985,7 +11147,7 @@
       </c>
     </row>
     <row r="24" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="N24" s="43" t="s">
+      <c r="N24" s="50" t="s">
         <v>39</v>
       </c>
       <c r="O24" s="1" t="s">
@@ -10994,14 +11156,14 @@
       <c r="P24" s="12">
         <v>76.03</v>
       </c>
-      <c r="R24" s="43"/>
+      <c r="R24" s="50"/>
       <c r="S24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="T24" s="14">
         <v>162.11000000000001</v>
       </c>
-      <c r="V24" s="43"/>
+      <c r="V24" s="50"/>
       <c r="W24" s="3" t="s">
         <v>23</v>
       </c>
@@ -11016,14 +11178,14 @@
       </c>
     </row>
     <row r="25" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="N25" s="43"/>
+      <c r="N25" s="50"/>
       <c r="O25" s="3" t="s">
         <v>22</v>
       </c>
       <c r="P25" s="14">
         <v>120.51</v>
       </c>
-      <c r="R25" s="43" t="s">
+      <c r="R25" s="50" t="s">
         <v>38</v>
       </c>
       <c r="S25" s="3" t="s">
@@ -11032,7 +11194,7 @@
       <c r="T25" s="14">
         <v>36.130000000000003</v>
       </c>
-      <c r="V25" s="43" t="s">
+      <c r="V25" s="50" t="s">
         <v>38</v>
       </c>
       <c r="W25" s="1" t="s">
@@ -11049,20 +11211,20 @@
       </c>
     </row>
     <row r="26" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A26" s="48" t="s">
+      <c r="A26" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="49"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="50"/>
-      <c r="N26" s="43" t="s">
+      <c r="B26" s="48"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="48"/>
+      <c r="K26" s="49"/>
+      <c r="N26" s="50" t="s">
         <v>40</v>
       </c>
       <c r="O26" s="1" t="s">
@@ -11071,14 +11233,14 @@
       <c r="P26" s="12">
         <v>67.260000000000005</v>
       </c>
-      <c r="R26" s="43"/>
+      <c r="R26" s="50"/>
       <c r="S26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="T26" s="14">
         <v>77.44</v>
       </c>
-      <c r="V26" s="43"/>
+      <c r="V26" s="50"/>
       <c r="W26" s="3" t="s">
         <v>22</v>
       </c>
@@ -11122,27 +11284,28 @@
       <c r="K27" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="N27" s="43"/>
+      <c r="N27" s="50"/>
       <c r="O27" s="3" t="s">
         <v>22</v>
       </c>
       <c r="P27" s="14">
         <v>109.92</v>
       </c>
-      <c r="R27" s="43"/>
+      <c r="R27" s="50"/>
       <c r="S27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="T27" s="14">
         <v>155.26</v>
       </c>
-      <c r="V27" s="43"/>
+      <c r="V27" s="50"/>
       <c r="W27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="X27" s="14">
         <v>83.87</v>
       </c>
+      <c r="AP27" s="55"/>
       <c r="BI27" s="9" t="s">
         <v>58</v>
       </c>
@@ -11170,7 +11333,7 @@
       <c r="I28" s="12"/>
       <c r="J28" s="13"/>
       <c r="K28" s="12"/>
-      <c r="N28" s="43" t="s">
+      <c r="N28" s="50" t="s">
         <v>41</v>
       </c>
       <c r="O28" s="1" t="s">
@@ -11179,7 +11342,7 @@
       <c r="P28" s="14">
         <v>66.27</v>
       </c>
-      <c r="R28" s="43" t="s">
+      <c r="R28" s="50" t="s">
         <v>39</v>
       </c>
       <c r="S28" s="3" t="s">
@@ -11188,7 +11351,7 @@
       <c r="T28" s="14">
         <v>103.04</v>
       </c>
-      <c r="V28" s="43" t="s">
+      <c r="V28" s="50" t="s">
         <v>39</v>
       </c>
       <c r="W28" s="1" t="s">
@@ -11228,21 +11391,21 @@
       <c r="I29" s="14"/>
       <c r="J29" s="16"/>
       <c r="K29" s="14"/>
-      <c r="N29" s="43"/>
+      <c r="N29" s="50"/>
       <c r="O29" s="3" t="s">
         <v>22</v>
       </c>
       <c r="P29" s="14">
         <v>40.51</v>
       </c>
-      <c r="R29" s="43"/>
+      <c r="R29" s="50"/>
       <c r="S29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="T29" s="14">
         <v>74.19</v>
       </c>
-      <c r="V29" s="43"/>
+      <c r="V29" s="50"/>
       <c r="W29" s="3" t="s">
         <v>22</v>
       </c>
@@ -11266,14 +11429,23 @@
       <c r="I30" s="14"/>
       <c r="J30" s="16"/>
       <c r="K30" s="14"/>
-      <c r="R30" s="43"/>
+      <c r="N30" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="O30" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="P30" s="52">
+        <v>67.010000000000005</v>
+      </c>
+      <c r="R30" s="50"/>
       <c r="S30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="T30" s="14">
         <v>37.31</v>
       </c>
-      <c r="V30" s="43"/>
+      <c r="V30" s="50"/>
       <c r="W30" s="3" t="s">
         <v>23</v>
       </c>
@@ -11301,7 +11473,14 @@
       </c>
       <c r="J31" s="16"/>
       <c r="K31" s="14"/>
-      <c r="R31" s="43" t="s">
+      <c r="N31" s="54"/>
+      <c r="O31" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P31" s="52">
+        <v>101.7</v>
+      </c>
+      <c r="R31" s="50" t="s">
         <v>40</v>
       </c>
       <c r="S31" s="3" t="s">
@@ -11310,7 +11489,7 @@
       <c r="T31" s="14">
         <v>81.790000000000006</v>
       </c>
-      <c r="V31" s="43" t="s">
+      <c r="V31" s="50" t="s">
         <v>40</v>
       </c>
       <c r="W31" s="1" t="s">
@@ -11338,14 +11517,14 @@
       <c r="I32" s="14"/>
       <c r="J32" s="16"/>
       <c r="K32" s="14"/>
-      <c r="R32" s="43"/>
+      <c r="R32" s="50"/>
       <c r="S32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="T32" s="14">
         <v>72.77</v>
       </c>
-      <c r="V32" s="43"/>
+      <c r="V32" s="50"/>
       <c r="W32" s="3" t="s">
         <v>22</v>
       </c>
@@ -11373,14 +11552,14 @@
       <c r="I33" s="12"/>
       <c r="J33" s="13"/>
       <c r="K33" s="12"/>
-      <c r="R33" s="43"/>
+      <c r="R33" s="50"/>
       <c r="S33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="T33" s="14">
         <v>28.61</v>
       </c>
-      <c r="V33" s="43"/>
+      <c r="V33" s="50"/>
       <c r="W33" s="3" t="s">
         <v>23</v>
       </c>
@@ -11421,7 +11600,7 @@
       <c r="P34" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="R34" s="43" t="s">
+      <c r="R34" s="50" t="s">
         <v>41</v>
       </c>
       <c r="S34" s="3" t="s">
@@ -11430,7 +11609,7 @@
       <c r="T34" s="14">
         <v>36.32</v>
       </c>
-      <c r="V34" s="43" t="s">
+      <c r="V34" s="50" t="s">
         <v>41</v>
       </c>
       <c r="W34" s="1" t="s">
@@ -11462,7 +11641,7 @@
       <c r="I35" s="14"/>
       <c r="J35" s="16"/>
       <c r="K35" s="14"/>
-      <c r="N35" s="43" t="s">
+      <c r="N35" s="50" t="s">
         <v>35</v>
       </c>
       <c r="O35" s="3" t="s">
@@ -11471,14 +11650,14 @@
       <c r="P35" s="14">
         <v>155.71</v>
       </c>
-      <c r="R35" s="43"/>
+      <c r="R35" s="50"/>
       <c r="S35" s="3" t="s">
         <v>24</v>
       </c>
       <c r="T35" s="14">
         <v>74.75</v>
       </c>
-      <c r="V35" s="43"/>
+      <c r="V35" s="50"/>
       <c r="W35" s="3" t="s">
         <v>22</v>
       </c>
@@ -11512,21 +11691,21 @@
       </c>
       <c r="J36" s="16"/>
       <c r="K36" s="14"/>
-      <c r="N36" s="43"/>
+      <c r="N36" s="50"/>
       <c r="O36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="P36" s="14">
         <v>243.65</v>
       </c>
-      <c r="R36" s="43"/>
+      <c r="R36" s="50"/>
       <c r="S36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="T36" s="14">
         <v>93.73</v>
       </c>
-      <c r="V36" s="43"/>
+      <c r="V36" s="50"/>
       <c r="W36" s="3" t="s">
         <v>23</v>
       </c>
@@ -11558,7 +11737,7 @@
       <c r="I37" s="14"/>
       <c r="J37" s="16"/>
       <c r="K37" s="14"/>
-      <c r="N37" s="43" t="s">
+      <c r="N37" s="50" t="s">
         <v>36</v>
       </c>
       <c r="O37" s="3" t="s">
@@ -11566,6 +11745,24 @@
       </c>
       <c r="P37" s="14">
         <v>120.93</v>
+      </c>
+      <c r="R37" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="S37" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="T37" s="52">
+        <v>88.13</v>
+      </c>
+      <c r="V37" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="W37" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="X37" s="52">
+        <v>68.61</v>
       </c>
     </row>
     <row r="38" spans="1:62" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -11588,12 +11785,23 @@
       <c r="I38" s="12"/>
       <c r="J38" s="13"/>
       <c r="K38" s="12"/>
-      <c r="N38" s="43"/>
+      <c r="N38" s="50"/>
       <c r="O38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="P38" s="14">
         <v>272.77</v>
+      </c>
+      <c r="R38" s="54"/>
+      <c r="S38" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="T38" s="52">
+        <v>74.819999999999993</v>
+      </c>
+      <c r="V38" s="54"/>
+      <c r="W38" s="51" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:62" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -11620,7 +11828,7 @@
       <c r="I39" s="14"/>
       <c r="J39" s="16"/>
       <c r="K39" s="14"/>
-      <c r="N39" s="43" t="s">
+      <c r="N39" s="50" t="s">
         <v>37</v>
       </c>
       <c r="O39" s="3" t="s">
@@ -11628,6 +11836,17 @@
       </c>
       <c r="P39" s="14">
         <v>120.93</v>
+      </c>
+      <c r="R39" s="54"/>
+      <c r="S39" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="T39" s="52">
+        <v>24.67</v>
+      </c>
+      <c r="V39" s="54"/>
+      <c r="W39" s="51" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:62" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -11646,7 +11865,7 @@
       <c r="I40" s="14"/>
       <c r="J40" s="16"/>
       <c r="K40" s="14"/>
-      <c r="N40" s="43"/>
+      <c r="N40" s="50"/>
       <c r="O40" s="3" t="s">
         <v>25</v>
       </c>
@@ -11677,7 +11896,7 @@
       </c>
       <c r="J41" s="16"/>
       <c r="K41" s="14"/>
-      <c r="N41" s="43" t="s">
+      <c r="N41" s="50" t="s">
         <v>38</v>
       </c>
       <c r="O41" s="3" t="s">
@@ -11711,7 +11930,7 @@
       <c r="I42" s="14"/>
       <c r="J42" s="16"/>
       <c r="K42" s="14"/>
-      <c r="N42" s="43"/>
+      <c r="N42" s="50"/>
       <c r="O42" s="3" t="s">
         <v>25</v>
       </c>
@@ -11745,7 +11964,7 @@
       <c r="I43" s="12"/>
       <c r="J43" s="13"/>
       <c r="K43" s="12"/>
-      <c r="N43" s="43" t="s">
+      <c r="N43" s="50" t="s">
         <v>39</v>
       </c>
       <c r="O43" s="3" t="s">
@@ -11785,7 +12004,7 @@
       <c r="I44" s="14"/>
       <c r="J44" s="16"/>
       <c r="K44" s="14"/>
-      <c r="N44" s="43"/>
+      <c r="N44" s="50"/>
       <c r="O44" s="3" t="s">
         <v>25</v>
       </c>
@@ -11815,7 +12034,7 @@
       <c r="I45" s="14"/>
       <c r="J45" s="16"/>
       <c r="K45" s="14"/>
-      <c r="N45" s="43" t="s">
+      <c r="N45" s="50" t="s">
         <v>40</v>
       </c>
       <c r="O45" s="3" t="s">
@@ -11851,7 +12070,7 @@
       </c>
       <c r="J46" s="16"/>
       <c r="K46" s="14"/>
-      <c r="N46" s="43"/>
+      <c r="N46" s="50"/>
       <c r="O46" s="3" t="s">
         <v>25</v>
       </c>
@@ -11883,7 +12102,7 @@
       <c r="I47" s="14"/>
       <c r="J47" s="16"/>
       <c r="K47" s="14"/>
-      <c r="N47" s="43" t="s">
+      <c r="N47" s="50" t="s">
         <v>41</v>
       </c>
       <c r="O47" s="3" t="s">
@@ -11919,15 +12138,21 @@
       <c r="I48" s="12"/>
       <c r="J48" s="13"/>
       <c r="K48" s="12"/>
-      <c r="N48" s="43"/>
+      <c r="N48" s="50"/>
       <c r="O48" s="3" t="s">
         <v>25</v>
       </c>
       <c r="P48" s="14">
         <v>238.53</v>
       </c>
+      <c r="S48" t="s">
+        <v>69</v>
+      </c>
+      <c r="T48" s="52">
+        <v>53.41</v>
+      </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A49" s="45"/>
       <c r="B49" s="3" t="s">
         <v>22</v>
@@ -11951,8 +12176,17 @@
       <c r="I49" s="14"/>
       <c r="J49" s="16"/>
       <c r="K49" s="14"/>
+      <c r="N49" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="O49" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="P49" s="52">
+        <v>115.68</v>
+      </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A50" s="45"/>
       <c r="B50" s="3" t="s">
         <v>23</v>
@@ -11968,8 +12202,15 @@
       <c r="I50" s="14"/>
       <c r="J50" s="16"/>
       <c r="K50" s="14"/>
+      <c r="N50" s="54"/>
+      <c r="O50" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="P50" s="52">
+        <v>202.98</v>
+      </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A51" s="45"/>
       <c r="B51" s="3" t="s">
         <v>24</v>
@@ -11990,7 +12231,7 @@
       <c r="J51" s="16"/>
       <c r="K51" s="14"/>
     </row>
-    <row r="52" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A52" s="45"/>
       <c r="B52" s="3" t="s">
         <v>25</v>
@@ -12009,7 +12250,7 @@
       <c r="J52" s="16"/>
       <c r="K52" s="14"/>
     </row>
-    <row r="53" spans="1:13" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:16" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A53" s="44" t="s">
         <v>14</v>
       </c>
@@ -12030,7 +12271,7 @@
       <c r="J53" s="13"/>
       <c r="K53" s="12"/>
     </row>
-    <row r="54" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A54" s="45"/>
       <c r="B54" s="3" t="s">
         <v>22</v>
@@ -12055,7 +12296,7 @@
       <c r="J54" s="16"/>
       <c r="K54" s="14"/>
     </row>
-    <row r="55" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A55" s="45"/>
       <c r="B55" s="3" t="s">
         <v>23</v>
@@ -12073,7 +12314,7 @@
       <c r="K55" s="14"/>
       <c r="M55" s="31"/>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A56" s="45"/>
       <c r="B56" s="3" t="s">
         <v>24</v>
@@ -12094,7 +12335,7 @@
       <c r="J56" s="16"/>
       <c r="K56" s="14"/>
     </row>
-    <row r="57" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A57" s="45"/>
       <c r="B57" s="3" t="s">
         <v>25</v>
@@ -12113,7 +12354,7 @@
       <c r="J57" s="16"/>
       <c r="K57" s="14"/>
     </row>
-    <row r="58" spans="1:13" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:16" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A58" s="44" t="s">
         <v>15</v>
       </c>
@@ -12134,7 +12375,7 @@
       <c r="J58" s="16"/>
       <c r="K58" s="14"/>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A59" s="45"/>
       <c r="B59" s="3" t="s">
         <v>22</v>
@@ -12159,7 +12400,7 @@
       <c r="J59" s="16"/>
       <c r="K59" s="14"/>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A60" s="45"/>
       <c r="B60" s="3" t="s">
         <v>23</v>
@@ -12176,7 +12417,7 @@
       <c r="J60" s="16"/>
       <c r="K60" s="14"/>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A61" s="45"/>
       <c r="B61" s="3" t="s">
         <v>24</v>
@@ -12197,7 +12438,7 @@
       <c r="J61" s="16"/>
       <c r="K61" s="14"/>
     </row>
-    <row r="62" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A62" s="45"/>
       <c r="B62" s="3" t="s">
         <v>25</v>
@@ -12216,7 +12457,7 @@
       <c r="J62" s="16"/>
       <c r="K62" s="14"/>
     </row>
-    <row r="63" spans="1:13" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:16" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A63" s="44" t="s">
         <v>67</v>
       </c>
@@ -12237,7 +12478,7 @@
       <c r="J63" s="12"/>
       <c r="K63" s="12"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A64" s="45"/>
       <c r="B64" s="3" t="s">
         <v>22</v>
@@ -12321,22 +12562,22 @@
     <row r="68" spans="1:20" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
     <row r="69" spans="1:20" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="70" spans="1:20" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A70" s="48" t="s">
+      <c r="A70" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="B70" s="49"/>
-      <c r="C70" s="49"/>
-      <c r="D70" s="49"/>
-      <c r="E70" s="49"/>
-      <c r="F70" s="49"/>
-      <c r="G70" s="49"/>
-      <c r="H70" s="49"/>
-      <c r="I70" s="49"/>
-      <c r="J70" s="49"/>
-      <c r="K70" s="49"/>
-      <c r="L70" s="49"/>
-      <c r="M70" s="49"/>
-      <c r="N70" s="50"/>
+      <c r="B70" s="48"/>
+      <c r="C70" s="48"/>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
+      <c r="J70" s="48"/>
+      <c r="K70" s="48"/>
+      <c r="L70" s="48"/>
+      <c r="M70" s="48"/>
+      <c r="N70" s="49"/>
     </row>
     <row r="71" spans="1:20" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A71" s="8"/>
@@ -13752,12 +13993,37 @@
     </row>
     <row r="104" spans="1:20" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <mergeCells count="47">
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A28:A32"/>
-    <mergeCell ref="A33:A37"/>
-    <mergeCell ref="A38:A42"/>
-    <mergeCell ref="A43:A47"/>
+  <mergeCells count="51">
+    <mergeCell ref="V34:V36"/>
+    <mergeCell ref="R31:R33"/>
+    <mergeCell ref="R34:R36"/>
+    <mergeCell ref="N30:N31"/>
+    <mergeCell ref="N49:N50"/>
+    <mergeCell ref="R37:R39"/>
+    <mergeCell ref="V37:V39"/>
+    <mergeCell ref="N35:N36"/>
+    <mergeCell ref="V16:V18"/>
+    <mergeCell ref="V19:V21"/>
+    <mergeCell ref="V22:V24"/>
+    <mergeCell ref="V25:V27"/>
+    <mergeCell ref="V28:V30"/>
+    <mergeCell ref="R22:R24"/>
+    <mergeCell ref="R25:R27"/>
+    <mergeCell ref="R28:R30"/>
+    <mergeCell ref="N22:N23"/>
+    <mergeCell ref="N24:N25"/>
+    <mergeCell ref="N26:N27"/>
+    <mergeCell ref="N28:N29"/>
+    <mergeCell ref="R16:R18"/>
+    <mergeCell ref="R19:R21"/>
+    <mergeCell ref="V31:V33"/>
+    <mergeCell ref="A63:A67"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="N37:N38"/>
+    <mergeCell ref="N39:N40"/>
+    <mergeCell ref="A92:A95"/>
+    <mergeCell ref="N45:N46"/>
+    <mergeCell ref="N41:N42"/>
     <mergeCell ref="A96:A99"/>
     <mergeCell ref="A100:A103"/>
     <mergeCell ref="A13:G13"/>
@@ -13774,32 +14040,11 @@
     <mergeCell ref="N18:N19"/>
     <mergeCell ref="N20:N21"/>
     <mergeCell ref="N43:N44"/>
-    <mergeCell ref="A63:A67"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="N37:N38"/>
-    <mergeCell ref="N39:N40"/>
-    <mergeCell ref="A92:A95"/>
-    <mergeCell ref="N45:N46"/>
-    <mergeCell ref="N41:N42"/>
-    <mergeCell ref="N35:N36"/>
-    <mergeCell ref="V16:V18"/>
-    <mergeCell ref="V19:V21"/>
-    <mergeCell ref="V22:V24"/>
-    <mergeCell ref="V25:V27"/>
-    <mergeCell ref="V28:V30"/>
-    <mergeCell ref="R22:R24"/>
-    <mergeCell ref="R25:R27"/>
-    <mergeCell ref="R28:R30"/>
-    <mergeCell ref="N22:N23"/>
-    <mergeCell ref="N24:N25"/>
-    <mergeCell ref="N26:N27"/>
-    <mergeCell ref="N28:N29"/>
-    <mergeCell ref="R16:R18"/>
-    <mergeCell ref="R19:R21"/>
-    <mergeCell ref="V31:V33"/>
-    <mergeCell ref="V34:V36"/>
-    <mergeCell ref="R31:R33"/>
-    <mergeCell ref="R34:R36"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A28:A32"/>
+    <mergeCell ref="A33:A37"/>
+    <mergeCell ref="A38:A42"/>
+    <mergeCell ref="A43:A47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
